--- a/astro-site/public/dl/guia-panaderia-obrador/checklist-appcc.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/checklist-appcc.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPCC Obrador" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'APPCC Obrador'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +44,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -83,10 +90,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -446,9 +464,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -465,10 +483,11 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -498,10 +517,6 @@
           <t>RECEPCIÓN MATERIAS PRIMAS</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,7 +593,6 @@
           <t>Hoja recepción</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -613,10 +627,6 @@
           <t>ALMACÉN Y SILOS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -720,7 +730,6 @@
           <t>Termómetro registro</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -755,10 +764,6 @@
           <t>MANIPULACIÓN MASA MADRE</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -835,7 +840,6 @@
           <t>Hoja masa madre</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -858,7 +862,6 @@
           <t>Etiqueta</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -866,10 +869,6 @@
           <t>FERMENTACIÓN</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -892,7 +891,6 @@
           <t>Termómetro registro</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -942,7 +940,6 @@
           <t>Higrómetro</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -950,10 +947,6 @@
           <t>HORNEADO</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -976,7 +969,6 @@
           <t>Termómetro sonda</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -999,7 +991,6 @@
           <t>Receta + timer</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1007,10 +998,6 @@
           <t>ALÉRGENOS Y CONTAMINACIÓN CRUZADA</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1060,7 +1047,6 @@
           <t>Etiqueta visible</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1122,10 +1108,6 @@
           <t>LIMPIEZA E HIGIENE PERSONAL</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1148,7 +1130,6 @@
           <t>Cartel + autoauditoría</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1171,7 +1152,6 @@
           <t>Foto inicio jornada</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1194,7 +1174,6 @@
           <t>Hoja limpieza</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1217,7 +1196,6 @@
           <t>Hoja limpieza</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1240,7 +1218,6 @@
           <t>Hoja limpieza</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1248,10 +1225,6 @@
           <t>DEVOLUCIÓN Y MERMAS</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1274,7 +1247,6 @@
           <t>Caja</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1297,7 +1269,6 @@
           <t>Albarán donación</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1320,7 +1291,27 @@
           <t>Cubeta merma</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C43">
+        <f>COUNTIF(A4:A41,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>COUNTIF(B4:B41,"?*")</f>
+        <v>30.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1334,6 +1325,25 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A32:E32"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A4:E41">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A4="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A10 A11 A12 A13 A14 A16 A17 A18 A19 A21 A22 A23 A25 A26 A28 A29 A30 A31 A33 A34 A35 A36 A37 A39 A40 A41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>